--- a/Health/Diet.xlsx
+++ b/Health/Diet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brijeshluckria/Desktop/GIT/HomeDIY/Health/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D878C3F4-C93E-6742-8773-96932214F23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14818A74-F4BD-9346-AC4B-8110001D90EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="2" xr2:uid="{A6D84EA6-F4DC-7548-9AEA-7DB3B0B2FF87}"/>
   </bookViews>
@@ -18,8 +18,9 @@
     <sheet name="Week-3-Daily Diet" sheetId="6" r:id="rId3"/>
     <sheet name="Suppliment" sheetId="7" r:id="rId4"/>
     <sheet name="Calculation" sheetId="2" r:id="rId5"/>
-    <sheet name="Rules" sheetId="4" r:id="rId6"/>
-    <sheet name="Reason for not loosing Fat1" sheetId="8" r:id="rId7"/>
+    <sheet name="Progress" sheetId="9" r:id="rId6"/>
+    <sheet name="Rules" sheetId="4" r:id="rId7"/>
+    <sheet name="Reason for not loosing Fat1" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="134">
   <si>
     <t>Time</t>
   </si>
@@ -432,6 +433,18 @@
   </si>
   <si>
     <t xml:space="preserve">Weekend Eating and Snacks Eating </t>
+  </si>
+  <si>
+    <t>Total Weight</t>
+  </si>
+  <si>
+    <t>Body Fat %</t>
+  </si>
+  <si>
+    <t>Body Fat Weigh</t>
+  </si>
+  <si>
+    <t>Lean Weight</t>
   </si>
 </sst>
 </file>
@@ -480,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -493,6 +506,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2815,6 +2829,72 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{710FC643-568B-3044-B794-BD00E0B9CDC4}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.1640625" customWidth="1"/>
+    <col min="2" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1" s="6">
+        <v>46095</v>
+      </c>
+      <c r="C1" s="6">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2">
+        <v>173.7</v>
+      </c>
+      <c r="C2">
+        <v>178.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3">
+        <v>21.5</v>
+      </c>
+      <c r="C3">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="C4">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5">
+        <v>136.4</v>
+      </c>
+      <c r="C5">
+        <v>133.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E87890-9D95-0849-A56B-CF5840703BA6}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2860,7 +2940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B18129-5129-4F45-AE15-835139382106}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/Health/Diet.xlsx
+++ b/Health/Diet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brijeshluckria/Desktop/GIT/HomeDIY/Health/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14818A74-F4BD-9346-AC4B-8110001D90EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29AC964-A0AE-8D48-A6F9-490218841E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="2" xr2:uid="{A6D84EA6-F4DC-7548-9AEA-7DB3B0B2FF87}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="5" xr2:uid="{A6D84EA6-F4DC-7548-9AEA-7DB3B0B2FF87}"/>
   </bookViews>
   <sheets>
     <sheet name="Week-1-Daily Diet" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Rules" sheetId="4" r:id="rId7"/>
     <sheet name="Reason for not loosing Fat1" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="136">
   <si>
     <t>Time</t>
   </si>
@@ -445,6 +445,12 @@
   </si>
   <si>
     <t>Lean Weight</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>Goal - 15th May</t>
   </si>
 </sst>
 </file>
@@ -493,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -507,6 +513,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2830,22 +2840,30 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{710FC643-568B-3044-B794-BD00E0B9CDC4}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.1640625" customWidth="1"/>
     <col min="2" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" s="6">
         <v>46095</v>
       </c>
       <c r="C1" s="6">
         <v>46060</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>130</v>
       </c>
@@ -2855,8 +2873,11 @@
       <c r="C2">
         <v>178.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>131</v>
       </c>
@@ -2866,8 +2887,11 @@
       <c r="C3">
         <v>25.1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E3" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>132</v>
       </c>
@@ -2877,8 +2901,15 @@
       <c r="C4">
         <v>44.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4">
+        <f>(B4-C4)</f>
+        <v>-7.5</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>133</v>
       </c>
@@ -2887,6 +2918,13 @@
       </c>
       <c r="C5">
         <v>133.6</v>
+      </c>
+      <c r="D5">
+        <f>(B5-C5)</f>
+        <v>2.8000000000000114</v>
+      </c>
+      <c r="E5">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Health/Diet.xlsx
+++ b/Health/Diet.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29AC964-A0AE-8D48-A6F9-490218841E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="5" xr2:uid="{A6D84EA6-F4DC-7548-9AEA-7DB3B0B2FF87}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="2" xr2:uid="{A6D84EA6-F4DC-7548-9AEA-7DB3B0B2FF87}"/>
   </bookViews>
   <sheets>
     <sheet name="Week-1-Daily Diet" sheetId="1" r:id="rId1"/>
@@ -509,14 +509,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2093,14 +2093,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -2163,14 +2163,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -2273,14 +2273,14 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -2443,14 +2443,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -2493,14 +2493,14 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -2663,14 +2663,14 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
@@ -2793,14 +2793,14 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
@@ -2850,13 +2850,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B1" s="6">
+      <c r="B1" s="5">
         <v>46095</v>
       </c>
-      <c r="C1" s="6">
+      <c r="C1" s="5">
         <v>46060</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>134</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -2887,7 +2887,7 @@
       <c r="C3">
         <v>25.1</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>0.1</v>
       </c>
     </row>
